--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/주별 발주 W07.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/주별 발주 W07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,23 +424,23 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>주차</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>납기</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249</v>
+        <v>667</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -451,11 +451,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232</v>
+        <v>470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -466,11 +466,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153</v>
+        <v>706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -496,11 +496,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -511,11 +511,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>601</v>
+        <v>196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>801</v>
+        <v>453</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -556,11 +556,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>848</v>
+        <v>942</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>907</v>
+        <v>540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686</v>
+        <v>321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>236</v>
+        <v>175</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,11 +631,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>317</v>
+        <v>967</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -676,11 +676,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>943</v>
+        <v>876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>651</v>
+        <v>266</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -721,11 +721,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>447</v>
+        <v>660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>517</v>
+        <v>291</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>362</v>
+        <v>650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>697</v>
+        <v>639</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>814</v>
+        <v>105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>336</v>
+        <v>666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>436</v>
+        <v>616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>395</v>
+        <v>684</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>782</v>
+        <v>747</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>494</v>
+        <v>355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>879</v>
+        <v>52</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>317</v>
+        <v>93</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -916,11 +916,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>157</v>
+        <v>981</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -931,11 +931,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>946</v>
+        <v>799</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>585</v>
+        <v>281</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -961,11 +961,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>436</v>
+        <v>225</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -976,11 +976,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>552</v>
+        <v>436</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -991,11 +991,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>407</v>
+        <v>664</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1006,11 +1006,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>271</v>
+        <v>519</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>348</v>
+        <v>568</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>90</v>
+        <v>667</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877</v>
+        <v>504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>104</v>
+        <v>834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>751</v>
+        <v>425</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62</v>
+        <v>474</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1111,11 +1111,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>396</v>
+        <v>715</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1126,11 +1126,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>629</v>
+        <v>171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>50</v>
+        <v>435</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1156,11 +1156,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>751</v>
+        <v>358</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>582</v>
+        <v>157</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1201,11 +1201,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>500</v>
+        <v>892</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>900</v>
+        <v>336</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1231,11 +1231,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>320</v>
+        <v>891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>226</v>
+        <v>418</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1261,11 +1261,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>995</v>
+        <v>788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>130</v>
+        <v>537</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>782</v>
+        <v>118</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1306,11 +1306,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>946</v>
+        <v>257</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>722</v>
+        <v>135</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>730</v>
+        <v>470</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>416</v>
+        <v>154</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1366,11 +1366,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>575</v>
+        <v>61</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>804</v>
+        <v>978</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1396,11 +1396,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>399</v>
+        <v>894</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1411,11 +1411,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>556</v>
+        <v>438</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>377</v>
+        <v>995</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>277</v>
+        <v>843</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>535</v>
+        <v>966</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>487</v>
+        <v>748</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>832</v>
+        <v>204</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1516,11 +1516,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>946</v>
+        <v>488</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>389</v>
+        <v>910</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1546,11 +1546,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>433</v>
+        <v>519</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>586</v>
+        <v>102</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>769</v>
+        <v>527</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>999</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>576</v>
+        <v>230</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>603</v>
+        <v>371</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1655,1061 +1655,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>166</v>
+        <v>516</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>347</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>398</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>863</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>521</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>680</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>355</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>791</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>999</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>667</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>512</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>182</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>824</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>183</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>747</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>510</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>948</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>667</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>546</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>869</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>977</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>59</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>432</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>872</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>246</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>734</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>19</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>527</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>392</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>642</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>692</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>944</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>685</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>26</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>554</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>431</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>27</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>749</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>558</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>27</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>842</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>700</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>835</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>119</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>546</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>256</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>644</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>268</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>283</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>90</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>992</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>480</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>259</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>241</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>710</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>679</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>787</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>105</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>398</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>575</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>67</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>19</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>185</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>521</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>670</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>589</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>926</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>951</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>245</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>932</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>918</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
         </is>
       </c>
     </row>
